--- a/Share/Projects/ANG01_STOCK/exports/units/1/branding/ANG01 STOCK BRANDLIST A.6_M.2 #1 JB71 B,PNL DC PWR.xlsx
+++ b/Share/Projects/ANG01_STOCK/exports/units/1/branding/ANG01 STOCK BRANDLIST A.6_M.2 #1 JB71 B,PNL DC PWR.xlsx
@@ -73,7 +73,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -92,7 +92,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF2FF"/>
+        <fgColor rgb="FFE3E3E3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -110,12 +110,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF2FF"/>
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3E3E3"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -130,31 +136,174 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -530,25 +679,25 @@
       <c r="A2" s="4" t="str">
         <v/>
       </c>
-      <c r="B2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H2" s="2" t="str">
+      <c r="B2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -556,25 +705,25 @@
       <c r="A3" s="4" t="str">
         <v>Project #</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="5" t="str">
         <v>ANG01</v>
       </c>
-      <c r="C3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H3" s="2" t="str">
+      <c r="C3" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H3" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -582,25 +731,25 @@
       <c r="A4" s="4" t="str">
         <v>Project Name</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B4" s="5" t="str">
         <v>STOCK</v>
       </c>
-      <c r="C4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H4" s="2" t="str">
+      <c r="C4" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D4" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E4" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F4" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H4" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -608,25 +757,25 @@
       <c r="A5" s="4" t="str">
         <v>Revision</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="5" t="str">
         <v>A.6_M.2</v>
       </c>
-      <c r="C5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H5" s="2" t="str">
+      <c r="C5" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E5" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -634,25 +783,25 @@
       <c r="A6" s="4" t="str">
         <v/>
       </c>
-      <c r="B6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H6" s="2" t="str">
+      <c r="B6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G6" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H6" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -660,25 +809,25 @@
       <c r="A7" s="4" t="str">
         <v>Controls DE</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="5" t="str">
         <v>Poovarasan M</v>
       </c>
-      <c r="C7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H7" s="2" t="str">
+      <c r="C7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -686,25 +835,25 @@
       <c r="A8" s="4" t="str">
         <v>Phone:</v>
       </c>
-      <c r="B8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H8" s="2" t="str">
+      <c r="B8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H8" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -712,25 +861,25 @@
       <c r="A9" s="4" t="str">
         <v>Controls ME</v>
       </c>
-      <c r="B9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H9" s="2" t="str">
+      <c r="B9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H9" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -738,25 +887,25 @@
       <c r="A10" s="4" t="str">
         <v>Phone:</v>
       </c>
-      <c r="B10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H10" s="2" t="str">
+      <c r="B10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H10" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -764,82 +913,82 @@
       <c r="A11" s="4" t="str">
         <v/>
       </c>
-      <c r="B11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H11" s="2" t="str">
+      <c r="B11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H11" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="6" t="str">
         <v>From</v>
       </c>
-      <c r="B12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="C12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G12" s="5" t="str">
+      <c r="B12" s="6" t="str">
+        <v/>
+      </c>
+      <c r="C12" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E12" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F12" s="6" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="6" t="str">
         <v>To</v>
       </c>
-      <c r="H12" s="5" t="str">
+      <c r="H12" s="6" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="str">
+      <c r="A13" s="7" t="str">
         <v>Device ID</v>
       </c>
-      <c r="B13" s="6" t="str">
+      <c r="B13" s="7" t="str">
         <v>Wire No.</v>
       </c>
-      <c r="C13" s="6" t="str">
+      <c r="C13" s="7" t="str">
         <v>Wire ID</v>
       </c>
-      <c r="D13" s="6" t="str">
+      <c r="D13" s="7" t="str">
         <v>Gauge/Size</v>
       </c>
-      <c r="E13" s="6" t="str">
+      <c r="E13" s="7" t="str">
         <v>Length</v>
       </c>
-      <c r="F13" s="6" t="str">
+      <c r="F13" s="7" t="str">
         <v>Device ID</v>
       </c>
-      <c r="G13" s="6" t="str">
+      <c r="G13" s="7" t="str">
         <v>To Location</v>
       </c>
-      <c r="H13" s="6" t="str">
+      <c r="H13" s="7" t="str">
         <v>Bundle Name</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="str">
+      <c r="A14" s="8" t="str">
         <v>FU</v>
       </c>
       <c r="B14" s="8" t="str">
@@ -865,267 +1014,267 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G15" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H15" s="8" t="str">
+      <c r="A15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H15" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="str">
+      <c r="A16" s="6" t="str">
         <v>FU0011:LD</v>
       </c>
-      <c r="B16" s="9" t="str">
+      <c r="B16" s="6" t="str">
         <v>FU0011</v>
       </c>
-      <c r="C16" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D16" s="9" t="str">
+      <c r="C16" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D16" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E16" s="9" t="str">
+      <c r="E16" s="6" t="str">
         <v>60.0</v>
       </c>
-      <c r="F16" s="9" t="str">
+      <c r="F16" s="6" t="str">
         <v>UJ0131:+</v>
       </c>
-      <c r="G16" s="9" t="str">
+      <c r="G16" s="6" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H16" s="9" t="str">
+      <c r="H16" s="6" t="str">
         <v>FU0011</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="str">
+      <c r="A17" s="5" t="str">
         <v>FU0011:LI</v>
       </c>
-      <c r="B17" s="8" t="str">
+      <c r="B17" s="5" t="str">
         <v>QF7752POS</v>
       </c>
-      <c r="C17" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D17" s="8" t="str">
+      <c r="C17" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D17" s="5" t="str">
         <v>12</v>
       </c>
-      <c r="E17" s="8" t="str">
+      <c r="E17" s="5" t="str">
         <v>60.0</v>
       </c>
-      <c r="F17" s="8" t="str">
+      <c r="F17" s="5" t="str">
         <v>XT0011:1</v>
       </c>
-      <c r="G17" s="8" t="str">
+      <c r="G17" s="5" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H17" s="8" t="str">
+      <c r="H17" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H18" s="8" t="str">
+      <c r="A18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H18" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="str">
+      <c r="A19" s="6" t="str">
         <v>FU0004:LD</v>
       </c>
-      <c r="B19" s="9" t="str">
+      <c r="B19" s="6" t="str">
         <v>FU0004</v>
       </c>
-      <c r="C19" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D19" s="9" t="str">
+      <c r="C19" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D19" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="E19" s="9" t="str">
+      <c r="E19" s="6" t="str">
         <v>60.0</v>
       </c>
-      <c r="F19" s="9" t="str">
+      <c r="F19" s="6" t="str">
         <v>XT0004:1</v>
       </c>
-      <c r="G19" s="9" t="str">
+      <c r="G19" s="6" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H19" s="9" t="str">
+      <c r="H19" s="6" t="str">
         <v>FU0004</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="str">
+      <c r="A20" s="5" t="str">
         <v>FU0004:LI</v>
       </c>
-      <c r="B20" s="8" t="str">
+      <c r="B20" s="5" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C20" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D20" s="8" t="str">
+      <c r="C20" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D20" s="5" t="str">
         <v>14</v>
       </c>
-      <c r="E20" s="8" t="str">
+      <c r="E20" s="5" t="str">
         <v>60.0</v>
       </c>
-      <c r="F20" s="8" t="str">
+      <c r="F20" s="5" t="str">
         <v>XT0002:7</v>
       </c>
-      <c r="G20" s="8" t="str">
+      <c r="G20" s="5" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H20" s="8" t="str">
+      <c r="H20" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G21" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H21" s="8" t="str">
+      <c r="A21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="str">
+      <c r="A22" s="6" t="str">
         <v>FU0005:LD</v>
       </c>
-      <c r="B22" s="9" t="str">
+      <c r="B22" s="6" t="str">
         <v>FU0005</v>
       </c>
-      <c r="C22" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D22" s="9" t="str">
+      <c r="C22" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D22" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="E22" s="9" t="str">
+      <c r="E22" s="6" t="str">
         <v>60.0</v>
       </c>
-      <c r="F22" s="9" t="str">
+      <c r="F22" s="6" t="str">
         <v>XT0005:1</v>
       </c>
-      <c r="G22" s="9" t="str">
+      <c r="G22" s="6" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H22" s="9" t="str">
+      <c r="H22" s="6" t="str">
         <v>FU0005</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="str">
+      <c r="A23" s="5" t="str">
         <v>FU0005:LI</v>
       </c>
-      <c r="B23" s="8" t="str">
+      <c r="B23" s="5" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C23" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D23" s="8" t="str">
+      <c r="C23" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D23" s="5" t="str">
         <v>14</v>
       </c>
-      <c r="E23" s="8" t="str">
+      <c r="E23" s="5" t="str">
         <v>60.0</v>
       </c>
-      <c r="F23" s="8" t="str">
+      <c r="F23" s="5" t="str">
         <v>XT0002:7</v>
       </c>
-      <c r="G23" s="8" t="str">
+      <c r="G23" s="5" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H23" s="8" t="str">
+      <c r="H23" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H24" s="8" t="str">
+      <c r="A24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H24" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="str">
+      <c r="A25" s="8" t="str">
         <v>UJ</v>
       </c>
       <c r="B25" s="8" t="str">
@@ -1151,85 +1300,85 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G26" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H26" s="8" t="str">
+      <c r="A26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="str">
+      <c r="A27" s="6" t="str">
         <v>UJ0131:-</v>
       </c>
-      <c r="B27" s="9" t="str">
+      <c r="B27" s="6" t="str">
         <v>QF7752NEG</v>
       </c>
-      <c r="C27" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D27" s="9" t="str">
+      <c r="C27" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D27" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E27" s="9" t="str">
+      <c r="E27" s="6" t="str">
         <v>60.0</v>
       </c>
-      <c r="F27" s="9" t="str">
+      <c r="F27" s="6" t="str">
         <v>XT0011:2</v>
       </c>
-      <c r="G27" s="9" t="str">
+      <c r="G27" s="6" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H27" s="9" t="str">
+      <c r="H27" s="6" t="str">
         <v>UJ - XT</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G28" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H28" s="8" t="str">
+      <c r="A28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="str">
+      <c r="A29" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B29" s="8" t="str">
@@ -1255,111 +1404,111 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G30" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H30" s="8" t="str">
+      <c r="A30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="str">
+      <c r="A31" s="6" t="str">
         <v>XT0003:7</v>
       </c>
-      <c r="B31" s="9" t="str">
+      <c r="B31" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C31" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D31" s="9" t="str">
+      <c r="C31" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D31" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="E31" s="9" t="str">
+      <c r="E31" s="6" t="str">
         <v>60.0</v>
       </c>
-      <c r="F31" s="9" t="str">
+      <c r="F31" s="6" t="str">
         <v>XT0004:3</v>
       </c>
-      <c r="G31" s="9" t="str">
+      <c r="G31" s="6" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H31" s="9" t="str">
+      <c r="H31" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="str">
+      <c r="A32" s="5" t="str">
         <v>XT0005:3</v>
       </c>
-      <c r="B32" s="8" t="str">
+      <c r="B32" s="11" t="str">
         <v>-0V</v>
       </c>
-      <c r="C32" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D32" s="8" t="str">
+      <c r="C32" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D32" s="5" t="str">
         <v>14</v>
       </c>
-      <c r="E32" s="8" t="str">
+      <c r="E32" s="5" t="str">
         <v>60.0</v>
       </c>
-      <c r="F32" s="8" t="str">
+      <c r="F32" s="5" t="str">
         <v>XT0003:7</v>
       </c>
-      <c r="G32" s="8" t="str">
+      <c r="G32" s="5" t="str">
         <v>JB71 B,PNL DC PWR</v>
       </c>
-      <c r="H32" s="8" t="str">
+      <c r="H32" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G33" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H33" s="8" t="str">
+      <c r="A33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H33" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="str">
+      <c r="A34" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B34" s="8" t="str">
@@ -1385,163 +1534,163 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G35" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H35" s="8" t="str">
+      <c r="A35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="str">
+      <c r="A36" s="6" t="str">
         <v>XT0005:3</v>
       </c>
-      <c r="B36" s="9" t="str">
+      <c r="B36" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C36" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D36" s="9" t="str">
+      <c r="C36" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D36" s="6" t="str">
         <v>16</v>
       </c>
-      <c r="E36" s="9" t="str">
+      <c r="E36" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F36" s="9" t="str">
+      <c r="F36" s="6" t="str">
         <v>EL0101:2-</v>
       </c>
-      <c r="G36" s="9" t="str">
+      <c r="G36" s="6" t="str">
         <v>JB71 B,BOX CONTROL</v>
       </c>
-      <c r="H36" s="9" t="str">
+      <c r="H36" s="6" t="str">
         <v>XT0005</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="str">
+      <c r="A37" s="5" t="str">
         <v>XT0005:4</v>
       </c>
-      <c r="B37" s="8" t="str">
+      <c r="B37" s="11" t="str">
         <v>-0V</v>
       </c>
-      <c r="C37" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D37" s="8" t="str">
+      <c r="C37" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D37" s="5" t="str">
         <v>16</v>
       </c>
-      <c r="E37" s="8" t="str">
+      <c r="E37" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F37" s="8" t="str">
+      <c r="F37" s="5" t="str">
         <v>EL0100:2-</v>
       </c>
-      <c r="G37" s="8" t="str">
+      <c r="G37" s="5" t="str">
         <v>JB71 B,BOX CONTROL</v>
       </c>
-      <c r="H37" s="8" t="str">
+      <c r="H37" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="str">
+      <c r="A38" s="5" t="str">
         <v>XT0005:1</v>
       </c>
-      <c r="B38" s="8" t="str">
+      <c r="B38" s="5" t="str">
         <v>FU0005</v>
       </c>
-      <c r="C38" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D38" s="8" t="str">
+      <c r="C38" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D38" s="5" t="str">
         <v>16</v>
       </c>
-      <c r="E38" s="8" t="str">
+      <c r="E38" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F38" s="8" t="str">
+      <c r="F38" s="5" t="str">
         <v>EL0101:1+</v>
       </c>
-      <c r="G38" s="8" t="str">
+      <c r="G38" s="5" t="str">
         <v>JB71 B,BOX CONTROL</v>
       </c>
-      <c r="H38" s="8" t="str">
+      <c r="H38" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="str">
+      <c r="A39" s="5" t="str">
         <v>XT0005:2</v>
       </c>
-      <c r="B39" s="8" t="str">
+      <c r="B39" s="5" t="str">
         <v>FU0005</v>
       </c>
-      <c r="C39" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D39" s="8" t="str">
+      <c r="C39" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D39" s="5" t="str">
         <v>16</v>
       </c>
-      <c r="E39" s="8" t="str">
+      <c r="E39" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F39" s="8" t="str">
+      <c r="F39" s="5" t="str">
         <v>EL0100:1+</v>
       </c>
-      <c r="G39" s="8" t="str">
+      <c r="G39" s="5" t="str">
         <v>JB71 B,BOX CONTROL</v>
       </c>
-      <c r="H39" s="8" t="str">
+      <c r="H39" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G40" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H40" s="8" t="str">
+      <c r="A40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="str">
+      <c r="A41" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B41" s="8" t="str">
@@ -1567,137 +1716,137 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G42" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H42" s="8" t="str">
+      <c r="A42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="str">
+      <c r="A43" s="6" t="str">
         <v>XT0002:2</v>
       </c>
-      <c r="B43" s="9" t="str">
+      <c r="B43" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C43" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D43" s="9" t="str">
+      <c r="C43" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D43" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="E43" s="9" t="str">
+      <c r="E43" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F43" s="9" t="str">
+      <c r="F43" s="6" t="str">
         <v>XT0070:1</v>
       </c>
-      <c r="G43" s="9" t="str">
+      <c r="G43" s="6" t="str">
         <v>JB71 B,PNL CTRL1</v>
       </c>
-      <c r="H43" s="9" t="str">
+      <c r="H43" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G44" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H44" s="8" t="str">
+      <c r="A44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="str">
+      <c r="A45" s="6" t="str">
         <v>XT0003:2</v>
       </c>
-      <c r="B45" s="9" t="str">
+      <c r="B45" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C45" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D45" s="9" t="str">
+      <c r="C45" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D45" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E45" s="9" t="str">
+      <c r="E45" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F45" s="9" t="str">
+      <c r="F45" s="6" t="str">
         <v>XT0070:2</v>
       </c>
-      <c r="G45" s="9" t="str">
+      <c r="G45" s="6" t="str">
         <v>JB71 B,PNL CTRL1</v>
       </c>
-      <c r="H45" s="9" t="str">
+      <c r="H45" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G46" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H46" s="8" t="str">
+      <c r="A46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="str">
+      <c r="A47" s="8" t="str">
         <v>UJ</v>
       </c>
       <c r="B47" s="8" t="str">
@@ -1723,163 +1872,163 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G48" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H48" s="8" t="str">
+      <c r="A48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H48" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="str">
+      <c r="A49" s="6" t="str">
         <v>UJ0131:IOUT</v>
       </c>
-      <c r="B49" s="9" t="str">
+      <c r="B49" s="6" t="str">
         <v>UJ0131IOUT</v>
       </c>
-      <c r="C49" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D49" s="9" t="str">
+      <c r="C49" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D49" s="6" t="str">
         <v>20</v>
       </c>
-      <c r="E49" s="9" t="str">
+      <c r="E49" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F49" s="9" t="str">
+      <c r="F49" s="6" t="str">
         <v>AF0385:09</v>
       </c>
-      <c r="G49" s="9" t="str">
+      <c r="G49" s="6" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H49" s="9" t="str">
+      <c r="H49" s="6" t="str">
         <v>UJ0131</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="str">
+      <c r="A50" s="5" t="str">
         <v>UJ0131:OK1</v>
       </c>
-      <c r="B50" s="8" t="str">
+      <c r="B50" s="5" t="str">
         <v>UJ0131OK1</v>
       </c>
-      <c r="C50" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D50" s="8" t="str">
+      <c r="C50" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D50" s="5" t="str">
         <v>20</v>
       </c>
-      <c r="E50" s="8" t="str">
+      <c r="E50" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F50" s="8" t="str">
+      <c r="F50" s="5" t="str">
         <v>AF0061:41</v>
       </c>
-      <c r="G50" s="8" t="str">
+      <c r="G50" s="5" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H50" s="8" t="str">
+      <c r="H50" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="str">
+      <c r="A51" s="5" t="str">
         <v>UJ0131:OK2</v>
       </c>
-      <c r="B51" s="8" t="str">
+      <c r="B51" s="5" t="str">
         <v>UJ0131OK2</v>
       </c>
-      <c r="C51" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D51" s="8" t="str">
+      <c r="C51" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D51" s="5" t="str">
         <v>20</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F51" s="8" t="str">
+      <c r="F51" s="5" t="str">
         <v>AF0061:09</v>
       </c>
-      <c r="G51" s="8" t="str">
+      <c r="G51" s="5" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H51" s="8" t="str">
+      <c r="H51" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="str">
+      <c r="A52" s="5" t="str">
         <v>UJ0131:VIN</v>
       </c>
-      <c r="B52" s="8" t="str">
+      <c r="B52" s="5" t="str">
         <v>UJ0131VIN</v>
       </c>
-      <c r="C52" s="8" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D52" s="8" t="str">
+      <c r="C52" s="5" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D52" s="5" t="str">
         <v>20</v>
       </c>
-      <c r="E52" s="8" t="str">
+      <c r="E52" s="5" t="str">
         <v>120.0</v>
       </c>
-      <c r="F52" s="8" t="str">
+      <c r="F52" s="5" t="str">
         <v>AF0385:07</v>
       </c>
-      <c r="G52" s="8" t="str">
+      <c r="G52" s="5" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H52" s="8" t="str">
+      <c r="H52" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G53" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H53" s="8" t="str">
+      <c r="A53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="str">
+      <c r="A54" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B54" s="8" t="str">
@@ -1905,137 +2054,137 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G55" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H55" s="8" t="str">
+      <c r="A55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="str">
+      <c r="A56" s="6" t="str">
         <v>XT0002:2</v>
       </c>
-      <c r="B56" s="9" t="str">
+      <c r="B56" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C56" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D56" s="9" t="str">
+      <c r="C56" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D56" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E56" s="9" t="str">
+      <c r="E56" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F56" s="9" t="str">
+      <c r="F56" s="6" t="str">
         <v>FU0060:LI</v>
       </c>
-      <c r="G56" s="9" t="str">
+      <c r="G56" s="6" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H56" s="9" t="str">
+      <c r="H56" s="6" t="str">
         <v>XT - FU</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G57" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H57" s="8" t="str">
+      <c r="A57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="str">
+      <c r="A58" s="6" t="str">
         <v>XT0003:2</v>
       </c>
-      <c r="B58" s="9" t="str">
+      <c r="B58" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C58" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D58" s="9" t="str">
+      <c r="C58" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D58" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E58" s="9" t="str">
+      <c r="E58" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F58" s="9" t="str">
+      <c r="F58" s="6" t="str">
         <v>XT0060:1</v>
       </c>
-      <c r="G58" s="9" t="str">
+      <c r="G58" s="6" t="str">
         <v>JB71 B,PNL CTRL2</v>
       </c>
-      <c r="H58" s="9" t="str">
+      <c r="H58" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G59" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H59" s="8" t="str">
+      <c r="A59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="str">
+      <c r="A60" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B60" s="8" t="str">
@@ -2061,137 +2210,137 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H61" s="8" t="str">
+      <c r="A61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="str">
+      <c r="A62" s="6" t="str">
         <v>XT0002:4</v>
       </c>
-      <c r="B62" s="9" t="str">
+      <c r="B62" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C62" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D62" s="9" t="str">
+      <c r="C62" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D62" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E62" s="9" t="str">
+      <c r="E62" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F62" s="9" t="str">
+      <c r="F62" s="6" t="str">
         <v>FU0180:LI</v>
       </c>
-      <c r="G62" s="9" t="str">
+      <c r="G62" s="6" t="str">
         <v>JB71 B,PNL CUSTOMER</v>
       </c>
-      <c r="H62" s="9" t="str">
+      <c r="H62" s="6" t="str">
         <v>XT - FU</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G63" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H63" s="8" t="str">
+      <c r="A63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="str">
+      <c r="A64" s="6" t="str">
         <v>XT0003:4</v>
       </c>
-      <c r="B64" s="9" t="str">
+      <c r="B64" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C64" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D64" s="9" t="str">
+      <c r="C64" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D64" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E64" s="9" t="str">
+      <c r="E64" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F64" s="9" t="str">
+      <c r="F64" s="6" t="str">
         <v>XT0180:1</v>
       </c>
-      <c r="G64" s="9" t="str">
+      <c r="G64" s="6" t="str">
         <v>JB71 B,PNL CUSTOMER</v>
       </c>
-      <c r="H64" s="9" t="str">
+      <c r="H64" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G65" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H65" s="8" t="str">
+      <c r="A65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H65" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="str">
+      <c r="A66" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B66" s="8" t="str">
@@ -2217,137 +2366,137 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G67" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H67" s="8" t="str">
+      <c r="A67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H67" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="str">
+      <c r="A68" s="6" t="str">
         <v>XT0002:4</v>
       </c>
-      <c r="B68" s="9" t="str">
+      <c r="B68" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C68" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D68" s="9" t="str">
+      <c r="C68" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D68" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E68" s="9" t="str">
+      <c r="E68" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F68" s="9" t="str">
+      <c r="F68" s="6" t="str">
         <v>FU0120:LI</v>
       </c>
-      <c r="G68" s="9" t="str">
+      <c r="G68" s="6" t="str">
         <v>JB71 B,PNL GEN CTRL</v>
       </c>
-      <c r="H68" s="9" t="str">
+      <c r="H68" s="6" t="str">
         <v>XT - FU</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G69" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H69" s="8" t="str">
+      <c r="A69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H69" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="str">
+      <c r="A70" s="6" t="str">
         <v>XT0003:4</v>
       </c>
-      <c r="B70" s="9" t="str">
+      <c r="B70" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C70" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D70" s="9" t="str">
+      <c r="C70" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D70" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E70" s="9" t="str">
+      <c r="E70" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F70" s="9" t="str">
+      <c r="F70" s="6" t="str">
         <v>XT0120:1</v>
       </c>
-      <c r="G70" s="9" t="str">
+      <c r="G70" s="6" t="str">
         <v>JB71 B,PNL GEN CTRL</v>
       </c>
-      <c r="H70" s="9" t="str">
+      <c r="H70" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G71" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H71" s="8" t="str">
+      <c r="A71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H71" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="str">
+      <c r="A72" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B72" s="8" t="str">
@@ -2373,137 +2522,137 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G73" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H73" s="8" t="str">
+      <c r="A73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H73" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="str">
+      <c r="A74" s="6" t="str">
         <v>XT0002:3</v>
       </c>
-      <c r="B74" s="9" t="str">
+      <c r="B74" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C74" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D74" s="9" t="str">
+      <c r="C74" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D74" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="E74" s="9" t="str">
+      <c r="E74" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F74" s="9" t="str">
+      <c r="F74" s="6" t="str">
         <v>FU0400:LI</v>
       </c>
-      <c r="G74" s="9" t="str">
+      <c r="G74" s="6" t="str">
         <v>JB71 B,PNL VIBRATION</v>
       </c>
-      <c r="H74" s="9" t="str">
+      <c r="H74" s="6" t="str">
         <v>XT - FU</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G75" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H75" s="8" t="str">
+      <c r="A75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H75" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="str">
+      <c r="A76" s="6" t="str">
         <v>XT0003:3</v>
       </c>
-      <c r="B76" s="9" t="str">
+      <c r="B76" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C76" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D76" s="9" t="str">
+      <c r="C76" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D76" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E76" s="9" t="str">
+      <c r="E76" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F76" s="9" t="str">
+      <c r="F76" s="6" t="str">
         <v>XT0401:1</v>
       </c>
-      <c r="G76" s="9" t="str">
+      <c r="G76" s="6" t="str">
         <v>JB71 B,PNL VIBRATION</v>
       </c>
-      <c r="H76" s="9" t="str">
+      <c r="H76" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G77" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H77" s="8" t="str">
+      <c r="A77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H77" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="str">
+      <c r="A78" s="8" t="str">
         <v>XT</v>
       </c>
       <c r="B78" s="8" t="str">
@@ -2529,106 +2678,106 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G79" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H79" s="8" t="str">
+      <c r="A79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H79" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="str">
+      <c r="A80" s="6" t="str">
         <v>XT0002:3</v>
       </c>
-      <c r="B80" s="9" t="str">
+      <c r="B80" s="6" t="str">
         <v>FU0136</v>
       </c>
-      <c r="C80" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D80" s="9" t="str">
+      <c r="C80" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D80" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E80" s="9" t="str">
+      <c r="E80" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F80" s="9" t="str">
+      <c r="F80" s="6" t="str">
         <v>FU0170:LI</v>
       </c>
-      <c r="G80" s="9" t="str">
+      <c r="G80" s="6" t="str">
         <v>JB71 C,PNL EQP PWR</v>
       </c>
-      <c r="H80" s="9" t="str">
+      <c r="H80" s="6" t="str">
         <v>XT - FU</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="D81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="G81" s="8" t="str">
-        <v/>
-      </c>
-      <c r="H81" s="8" t="str">
+      <c r="A81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H81" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="str">
+      <c r="A82" s="6" t="str">
         <v>XT0003:3</v>
       </c>
-      <c r="B82" s="9" t="str">
+      <c r="B82" s="10" t="str">
         <v>-0V</v>
       </c>
-      <c r="C82" s="9" t="str">
-        <v>WHT</v>
-      </c>
-      <c r="D82" s="9" t="str">
+      <c r="C82" s="6" t="str">
+        <v>WHT</v>
+      </c>
+      <c r="D82" s="6" t="str">
         <v>12</v>
       </c>
-      <c r="E82" s="9" t="str">
+      <c r="E82" s="6" t="str">
         <v>120.0</v>
       </c>
-      <c r="F82" s="9" t="str">
+      <c r="F82" s="6" t="str">
         <v>XT0175:1</v>
       </c>
-      <c r="G82" s="9" t="str">
+      <c r="G82" s="6" t="str">
         <v>JB71 C,PNL EQP PWR</v>
       </c>
-      <c r="H82" s="9" t="str">
+      <c r="H82" s="6" t="str">
         <v>XT - XT</v>
       </c>
     </row>
